--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
